--- a/Table_S9.xlsx
+++ b/Table_S9.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S9_methylation" sheetId="1" r:id="R86f877c889c74f24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S9B_statistics" sheetId="2" r:id="Rd5865daf6505415a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S9C_ordinary_TE_control" sheetId="3" r:id="Rbf03c4a4c52040e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S9_methylation" sheetId="1" r:id="R8e24c33aa4eb4192"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S9B_statistics" sheetId="2" r:id="R0267e036b032436a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S9C_ordinary_TE_control" sheetId="3" r:id="Rb63b3e376c3c48a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S9D_selected_outliers" sheetId="4" r:id="Rbab903db3f994c14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +19,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="0.00000"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -45,8 +46,27 @@
       <x:color rgb="FF000000"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -73,8 +93,13 @@
         <x:fgColor rgb="FFD9DDE3"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9DCE1"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="6">
+  <x:borders count="7">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -133,11 +158,16 @@
         <x:color rgb="FFD9D9D9"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -211,6 +241,40 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -347,9 +411,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -986,7 +1050,159 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra67a9b0514e24daa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7cf3d024a3c4972"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="31" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="54" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="42" customHeight="1">
+      <x:c r="A1" s="39" t="str">
+        <x:v>Table S9. Public Col-0 leaf weighted methylation summaries for ONSEN terminal candidate windows, HSF-rich non-ONSEN TE outliers and ordinary background TEs.</x:v>
+      </x:c>
+      <x:c r="B1" s="39"/>
+      <x:c r="C1" s="39"/>
+      <x:c r="D1" s="39"/>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="37" t="str">
+        <x:v>TE family / alias</x:v>
+      </x:c>
+      <x:c r="B2" s="37" t="str">
+        <x:v>TAIR TE identifier</x:v>
+      </x:c>
+      <x:c r="C2" s="37" t="str">
+        <x:v>Downstream analysis set</x:v>
+      </x:c>
+      <x:c r="D2" s="37" t="str">
+        <x:v>Selection note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="34" customHeight="1">
+      <x:c r="A3" s="38" t="str">
+        <x:v>ATCOPIA88</x:v>
+      </x:c>
+      <x:c r="B3" s="38" t="str">
+        <x:v>AT1TE36340</x:v>
+      </x:c>
+      <x:c r="C3" s="38" t="str">
+        <x:v>Figs 4B-D and 5C; Tables S9-S10</x:v>
+      </x:c>
+      <x:c r="D3" s="38" t="str">
+        <x:v>Included in the fixed eight-region HSF-rich non-ONSEN TE subset.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="34" customHeight="1">
+      <x:c r="A4" s="38" t="str">
+        <x:v>ATHILA4A</x:v>
+      </x:c>
+      <x:c r="B4" s="38" t="str">
+        <x:v>AT1TE44520</x:v>
+      </x:c>
+      <x:c r="C4" s="38" t="str">
+        <x:v>Figs 4B-D and 5C; Tables S9-S10</x:v>
+      </x:c>
+      <x:c r="D4" s="38" t="str">
+        <x:v>Included in the fixed eight-region HSF-rich non-ONSEN TE subset.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="34" customHeight="1">
+      <x:c r="A5" s="38" t="str">
+        <x:v>ATHILA8B</x:v>
+      </x:c>
+      <x:c r="B5" s="38" t="str">
+        <x:v>AT5TE37570</x:v>
+      </x:c>
+      <x:c r="C5" s="38" t="str">
+        <x:v>Figs 4B-D and 5C; Tables S9-S10</x:v>
+      </x:c>
+      <x:c r="D5" s="38" t="str">
+        <x:v>Included in the fixed eight-region HSF-rich non-ONSEN TE subset.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="34" customHeight="1">
+      <x:c r="A6" s="38" t="str">
+        <x:v>ATHILA4A</x:v>
+      </x:c>
+      <x:c r="B6" s="38" t="str">
+        <x:v>AT5TE45145</x:v>
+      </x:c>
+      <x:c r="C6" s="38" t="str">
+        <x:v>Figs 4B-D and 5C; Tables S9-S10</x:v>
+      </x:c>
+      <x:c r="D6" s="38" t="str">
+        <x:v>Included in the fixed eight-region HSF-rich non-ONSEN TE subset.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="34" customHeight="1">
+      <x:c r="A7" s="38" t="str">
+        <x:v>ATHILA4A</x:v>
+      </x:c>
+      <x:c r="B7" s="38" t="str">
+        <x:v>AT1TE51750</x:v>
+      </x:c>
+      <x:c r="C7" s="38" t="str">
+        <x:v>Figs 4B-D and 5C; Tables S9-S10</x:v>
+      </x:c>
+      <x:c r="D7" s="38" t="str">
+        <x:v>Included in the fixed eight-region HSF-rich non-ONSEN TE subset.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="34" customHeight="1">
+      <x:c r="A8" s="38" t="str">
+        <x:v>ATHILA4D</x:v>
+      </x:c>
+      <x:c r="B8" s="38" t="str">
+        <x:v>AT2TE49215</x:v>
+      </x:c>
+      <x:c r="C8" s="38" t="str">
+        <x:v>Figs 4B-D and 5C; Tables S9-S10</x:v>
+      </x:c>
+      <x:c r="D8" s="38" t="str">
+        <x:v>Included in the fixed eight-region HSF-rich non-ONSEN TE subset.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="A9" s="38" t="str">
+        <x:v>ATHILA4A</x:v>
+      </x:c>
+      <x:c r="B9" s="38" t="str">
+        <x:v>AT1TE47330</x:v>
+      </x:c>
+      <x:c r="C9" s="38" t="str">
+        <x:v>Figs 4B-D and 5C; Tables S9-S10</x:v>
+      </x:c>
+      <x:c r="D9" s="38" t="str">
+        <x:v>Included in the fixed eight-region HSF-rich non-ONSEN TE subset.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="34" customHeight="1">
+      <x:c r="A10" s="38" t="str">
+        <x:v>ATHILA4A</x:v>
+      </x:c>
+      <x:c r="B10" s="38" t="str">
+        <x:v>AT1TE47115</x:v>
+      </x:c>
+      <x:c r="C10" s="38" t="str">
+        <x:v>Figs 4B-D and 5C; Tables S9-S10</x:v>
+      </x:c>
+      <x:c r="D10" s="38" t="str">
+        <x:v>Included in the fixed eight-region HSF-rich non-ONSEN TE subset.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>